--- a/simulations/correction_peat_market/AS_marché/AS_marché_hobby/inv/AS_neg_inv_mark_VF2.xlsx
+++ b/simulations/correction_peat_market/AS_marché/AS_marché_hobby/inv/AS_neg_inv_mark_VF2.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\AS_marché\AS_marché_hobby\inv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011723E9-52D7-48C6-B579-17EE964D8F40}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7AD8FDE-20A9-4877-9857-69329E58B8BD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
@@ -267,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -280,11 +283,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -301,6 +313,35 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="results"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="AK3">
+            <v>-651101.69874275697</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="AL4">
+            <v>-684134.54392147798</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="AM5">
+            <v>-6.3578543683243343</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -588,67 +629,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="6"/>
+      <c r="C1" s="7"/>
       <c r="D1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="7"/>
       <c r="Z1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="7"/>
       <c r="AC1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="AD1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="AE1" s="6"/>
+      <c r="AE1" s="7"/>
       <c r="AF1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AG1" s="6"/>
+      <c r="AG1" s="7"/>
       <c r="AH1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="AI1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AJ1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="AK1" s="7"/>
-      <c r="AL1" s="7"/>
-      <c r="AM1" s="7"/>
-      <c r="AN1" s="7"/>
-      <c r="AO1" s="6"/>
+      <c r="AK1" s="9"/>
+      <c r="AL1" s="9"/>
+      <c r="AM1" s="9"/>
+      <c r="AN1" s="9"/>
+      <c r="AO1" s="10"/>
     </row>
     <row r="2" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -1248,9 +1289,22 @@
         <v>100</v>
       </c>
     </row>
+    <row r="11" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="AK11" s="4">
+        <f>(AK3-[1]results!$AK$3)/[1]results!$AK$3</f>
+        <v>-9.0949048208555594E-2</v>
+      </c>
+      <c r="AL11" s="4">
+        <f>(AL4-[1]results!$AL$4)/[1]results!$AL$4</f>
+        <v>-4.6815421026011397E-2</v>
+      </c>
+      <c r="AM11" s="4">
+        <f>(AM5-[1]results!$AM$5)/[1]results!$AM$5</f>
+        <v>-5.1899540064389356E-2</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="AJ1:AO1"/>
+  <mergeCells count="5">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:Y1"/>
     <mergeCell ref="Z1:AB1"/>
